--- a/docs/features/quickfile-cash-basis/MTD_SA103_2026-27_Q1_6Apr-5Jul.xlsx
+++ b/docs/features/quickfile-cash-basis/MTD_SA103_2026-27_Q1_6Apr-5Jul.xlsx
@@ -808,7 +808,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="18">
-        <v>16256.24</v>
+        <v>16287.73</v>
       </c>
       <c r="D7" s="19"/>
       <c r="F7" s="20"/>
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="43">
-        <v>114.34</v>
+        <v>114.82</v>
       </c>
       <c r="D47" s="19"/>
       <c r="F47" s="20"/>
@@ -1535,7 +1535,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="43">
-        <v>1984.31</v>
+        <v>1986.57</v>
       </c>
       <c r="D75" s="19"/>
       <c r="F75" s="20"/>

--- a/docs/features/quickfile-cash-basis/MTD_SA103_2026-27_Q1_6Apr-5Jul.xlsx
+++ b/docs/features/quickfile-cash-basis/MTD_SA103_2026-27_Q1_6Apr-5Jul.xlsx
@@ -808,7 +808,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="18">
-        <v>16287.73</v>
+        <v>16423.34</v>
       </c>
       <c r="D7" s="19"/>
       <c r="F7" s="20"/>
@@ -1535,7 +1535,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="43">
-        <v>1986.57</v>
+        <v>1987.70</v>
       </c>
       <c r="D75" s="19"/>
       <c r="F75" s="20"/>
